--- a/data/lot-details.xlsx
+++ b/data/lot-details.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="12975"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="138">
   <si>
     <t>进口批次 / 货品</t>
   </si>
@@ -35,6 +35,21 @@
     <t>进口发票金额 (USD)</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="DengXian"/>
+        <charset val="134"/>
+      </rPr>
+      <t>货款已付</t>
+    </r>
+  </si>
+  <si>
     <t>出口批次&lt;br&gt;(Export Lot)</t>
   </si>
   <si>
@@ -110,12 +125,43 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池模组</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
     <t>Export Lot 1</t>
   </si>
   <si>
     <t>单层平铺 (20托)</t>
   </si>
   <si>
+    <t>#########</t>
+  </si>
+  <si>
     <t>1月26日</t>
   </si>
   <si>
@@ -155,6 +201,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池模组</t>
+    </r>
+  </si>
+  <si>
     <t>2月2日</t>
   </si>
   <si>
@@ -182,6 +242,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;纯电芯*(已剥离模组)*</t>
+    </r>
+  </si>
+  <si>
     <t>Export Lot 2</t>
   </si>
   <si>
@@ -224,6 +298,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>Export Lot 3</t>
   </si>
   <si>
@@ -269,6 +357,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>Export Lot 5</t>
   </si>
   <si>
@@ -308,6 +410,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>Export Lot 7</t>
   </si>
   <si>
@@ -347,6 +463,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>Export Lot 4</t>
   </si>
   <si>
@@ -392,6 +522,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>待定 (TBD)</t>
   </si>
   <si>
@@ -425,6 +569,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>3月1日</t>
   </si>
   <si>
@@ -452,6 +610,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 10.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>Export Lot 6</t>
   </si>
   <si>
@@ -485,6 +657,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 10.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>5月1日</t>
   </si>
   <si>
@@ -512,13 +698,38 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>3月16日</t>
   </si>
   <si>
     <t>4月28日</t>
   </si>
   <si>
-    <t xml:space="preserve">MSK </t>
+    <r>
+      <t>MSK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
   <si>
     <t>5月17日</t>
@@ -548,36 +759,99 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Lot 12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>3月22日</t>
   </si>
   <si>
     <t>5月9日</t>
   </si>
   <si>
-    <t xml:space="preserve">Cosco </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
+    <r>
+      <t>Cosco</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5/18/2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="SimSun"/>
+        <charset val="0"/>
+      </rPr>
+      <t>暂定</t>
+    </r>
+  </si>
+  <si>
+    <t>正常在途</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF303030"/>
         <rFont val="1rem / 1.5rem google sans text"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">5/18/2026 </t>
+      <t>Lot 13</t>
     </r>
     <r>
       <rPr>
         <sz val="10.5"/>
         <color rgb="FF303030"/>
-        <rFont val="SimSun"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
         <charset val="134"/>
       </rPr>
-      <t>暂定</t>
-    </r>
-  </si>
-  <si>
-    <t>正常在途</t>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lot 13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>estimate 5/20</t>
+  </si>
+  <si>
+    <t>3月29日</t>
+  </si>
+  <si>
+    <t>5月12日</t>
   </si>
   <si>
     <r>
@@ -588,7 +862,7 @@
         <rFont val="1rem / 1.5rem google sans text"/>
         <charset val="134"/>
       </rPr>
-      <t>Lot 13</t>
+      <t>Lot 14</t>
     </r>
     <r>
       <rPr>
@@ -601,10 +875,27 @@
     </r>
   </si>
   <si>
-    <t>3月29日</t>
-  </si>
-  <si>
-    <t>5月12日</t>
+    <r>
+      <t>Lot 14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>4月9日</t>
+  </si>
+  <si>
+    <t>5月26日</t>
+  </si>
+  <si>
+    <t>头程延误 2 天</t>
   </si>
   <si>
     <r>
@@ -615,7 +906,7 @@
         <rFont val="1rem / 1.5rem google sans text"/>
         <charset val="134"/>
       </rPr>
-      <t>Lot 14</t>
+      <t>Lot 15</t>
     </r>
     <r>
       <rPr>
@@ -628,13 +919,24 @@
     </r>
   </si>
   <si>
-    <t>4月9日</t>
-  </si>
-  <si>
-    <t>5月26日</t>
-  </si>
-  <si>
-    <t>头程延误 2 天</t>
+    <r>
+      <t>Lot 15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>待确认</t>
+  </si>
+  <si>
+    <t>上游排期待跟进</t>
   </si>
   <si>
     <r>
@@ -645,7 +947,7 @@
         <rFont val="1rem / 1.5rem google sans text"/>
         <charset val="134"/>
       </rPr>
-      <t>Lot 15</t>
+      <t>Lot 16</t>
     </r>
     <r>
       <rPr>
@@ -658,28 +960,15 @@
     </r>
   </si>
   <si>
-    <t>待确认</t>
-  </si>
-  <si>
-    <t>上游排期待跟进</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
+    <r>
       <t>Lot 16</t>
     </r>
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
       </rPr>
       <t>&lt;br&gt;电池电芯</t>
     </r>
@@ -707,14 +996,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="#\ ??/??"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -730,10 +1020,35 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF333333"/>
+      <name val="1rem / 1.5rem google sans text"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FF303030"/>
       <name val="1rem / 1.5rem google sans text"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF333333"/>
+      <name val="1rem / 1.5rem google sans text"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
     </font>
     <font>
       <u/>
@@ -881,12 +1196,19 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF303030"/>
+      <color rgb="FF333333"/>
       <name val="SimSun"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF333333"/>
+      <name val="DengXian"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -901,20 +1223,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.4"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEDB61"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
@@ -1248,183 +1588,213 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="8" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="8" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="8" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="8" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="8" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1952,7 +2322,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.75" customWidth="1"/>
@@ -1966,1183 +2336,1386 @@
     <col min="20" max="20" width="24.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:20">
+    <row r="1" ht="15" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="W1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="14.25" spans="1:20">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="3">
+    <row r="2" ht="15" spans="1:25">
+      <c r="A2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="5">
         <v>399960</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="C2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="7">
+        <v>399960</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="9">
         <v>10</v>
       </c>
-      <c r="E2" s="4">
+      <c r="H2" s="9">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="I2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="9">
         <v>200</v>
       </c>
-      <c r="H2" s="5">
+      <c r="K2" s="10">
         <v>4000</v>
       </c>
-      <c r="I2" s="5">
+      <c r="L2" s="10">
         <v>96000</v>
       </c>
-      <c r="J2" s="5">
+      <c r="M2" s="10">
         <v>96000</v>
       </c>
-      <c r="K2" s="6">
+      <c r="N2" s="11">
         <v>121200</v>
       </c>
-      <c r="L2" s="6">
+      <c r="O2" s="11">
         <v>132000</v>
       </c>
-      <c r="M2" s="7">
+      <c r="P2" s="12">
         <v>4.7</v>
       </c>
-      <c r="N2" s="7">
-        <v>451200</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="Q2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+    </row>
+    <row r="3" ht="15" spans="1:25">
+      <c r="A3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="5">
+        <v>239976</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="7">
+        <v>239976</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="F3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="G3" s="9">
+        <v>6</v>
+      </c>
+      <c r="H3" s="9">
+        <v>6</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="J3" s="9">
+        <v>120</v>
+      </c>
+      <c r="K3" s="10">
+        <v>2400</v>
+      </c>
+      <c r="L3" s="10">
+        <v>57600</v>
+      </c>
+      <c r="M3" s="10">
+        <v>57600</v>
+      </c>
+      <c r="N3" s="11">
+        <v>72720</v>
+      </c>
+      <c r="O3" s="11">
+        <v>79200</v>
+      </c>
+      <c r="P3" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="Q3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="R3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
     </row>
-    <row r="3" ht="14.25" spans="1:20">
-      <c r="A3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="3">
-        <v>239976</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="4">
+    <row r="4" ht="15" spans="1:25">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5">
+        <v>161571.57</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="7">
+        <v>161571.57</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="9">
+        <v>8</v>
+      </c>
+      <c r="H4" s="9">
+        <v>4</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="9">
+        <v>158</v>
+      </c>
+      <c r="K4" s="10">
+        <v>2528</v>
+      </c>
+      <c r="L4" s="10">
+        <v>41312</v>
+      </c>
+      <c r="M4" s="10">
+        <v>40448</v>
+      </c>
+      <c r="N4" s="11">
+        <v>42188.8</v>
+      </c>
+      <c r="O4" s="11">
+        <v>52140</v>
+      </c>
+      <c r="P4" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+    </row>
+    <row r="5" ht="15" spans="1:25">
+      <c r="A5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="5">
+        <v>239953.92</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="7">
+        <v>239953.92</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="9">
+        <v>12</v>
+      </c>
+      <c r="H5" s="9">
         <v>6</v>
       </c>
-      <c r="E3" s="4">
+      <c r="I5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="9">
+        <v>240</v>
+      </c>
+      <c r="K5" s="10">
+        <v>3840</v>
+      </c>
+      <c r="L5" s="10">
+        <v>61440</v>
+      </c>
+      <c r="M5" s="10">
+        <v>61440</v>
+      </c>
+      <c r="N5" s="11">
+        <v>65740.8</v>
+      </c>
+      <c r="O5" s="11">
+        <v>79200</v>
+      </c>
+      <c r="P5" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+    </row>
+    <row r="6" ht="15" spans="1:25">
+      <c r="A6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="5">
+        <v>199961.6</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="7">
+        <v>199961.6</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="9">
+        <v>10</v>
+      </c>
+      <c r="H6" s="9">
+        <v>5</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="9">
+        <v>200</v>
+      </c>
+      <c r="K6" s="10">
+        <v>3200</v>
+      </c>
+      <c r="L6" s="10">
+        <v>51200</v>
+      </c>
+      <c r="M6" s="10">
+        <v>51200</v>
+      </c>
+      <c r="N6" s="11">
+        <v>54784</v>
+      </c>
+      <c r="O6" s="11">
+        <v>66000</v>
+      </c>
+      <c r="P6" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="U6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="V6" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="W6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+    </row>
+    <row r="7" ht="15" spans="1:25">
+      <c r="A7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="5">
+        <v>99980.8</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="7">
+        <v>99980.8</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="9">
+        <v>5</v>
+      </c>
+      <c r="H7" s="9">
+        <v>3</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="9">
+        <v>100</v>
+      </c>
+      <c r="K7" s="10">
+        <v>1600</v>
+      </c>
+      <c r="L7" s="10">
+        <v>25600</v>
+      </c>
+      <c r="M7" s="10">
+        <v>25600</v>
+      </c>
+      <c r="N7" s="11">
+        <v>27392</v>
+      </c>
+      <c r="O7" s="11">
+        <v>33000</v>
+      </c>
+      <c r="P7" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="U7" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="W7" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+    </row>
+    <row r="8" ht="15" spans="1:25">
+      <c r="A8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="5">
+        <v>139973.12</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="7">
+        <v>139973.12</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="9">
+        <v>7</v>
+      </c>
+      <c r="H8" s="9">
+        <v>4</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="9">
+        <v>140</v>
+      </c>
+      <c r="K8" s="10">
+        <v>2240</v>
+      </c>
+      <c r="L8" s="10">
+        <v>35840</v>
+      </c>
+      <c r="M8" s="10">
+        <v>35840</v>
+      </c>
+      <c r="N8" s="11">
+        <v>38348.8</v>
+      </c>
+      <c r="O8" s="11">
+        <v>46200</v>
+      </c>
+      <c r="P8" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="U8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="W8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+    </row>
+    <row r="9" ht="15" spans="1:25">
+      <c r="A9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="5">
+        <v>99980.8</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="7">
+        <v>99980.8</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="9">
+        <v>5</v>
+      </c>
+      <c r="H9" s="9">
+        <v>3</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="9">
+        <v>100</v>
+      </c>
+      <c r="K9" s="10">
+        <v>1600</v>
+      </c>
+      <c r="L9" s="10">
+        <v>25600</v>
+      </c>
+      <c r="M9" s="10">
+        <v>25600</v>
+      </c>
+      <c r="N9" s="11">
+        <v>27392</v>
+      </c>
+      <c r="O9" s="11">
+        <v>33000</v>
+      </c>
+      <c r="P9" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="U9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+    </row>
+    <row r="10" ht="15" spans="1:25">
+      <c r="A10" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="5">
+        <v>139973.12</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="7">
+        <v>139973.12</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="9">
+        <v>7</v>
+      </c>
+      <c r="H10" s="9">
+        <v>4</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="9">
+        <v>140</v>
+      </c>
+      <c r="K10" s="10">
+        <v>2240</v>
+      </c>
+      <c r="L10" s="10">
+        <v>35840</v>
+      </c>
+      <c r="M10" s="10">
+        <v>35840</v>
+      </c>
+      <c r="N10" s="11">
+        <v>38348.8</v>
+      </c>
+      <c r="O10" s="11">
+        <v>46200</v>
+      </c>
+      <c r="P10" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="U10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="V10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="W10" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+    </row>
+    <row r="11" ht="15" spans="1:25">
+      <c r="A11" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="5">
+        <v>159969.28</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="7">
+        <v>159969.28</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="9">
+        <v>8</v>
+      </c>
+      <c r="H11" s="9">
+        <v>4</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="9">
+        <v>160</v>
+      </c>
+      <c r="K11" s="10">
+        <v>2560</v>
+      </c>
+      <c r="L11" s="10">
+        <v>40960</v>
+      </c>
+      <c r="M11" s="10">
+        <v>40960</v>
+      </c>
+      <c r="N11" s="11">
+        <v>43827.2</v>
+      </c>
+      <c r="O11" s="11">
+        <v>52800</v>
+      </c>
+      <c r="P11" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="U11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="V11" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="W11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" ht="15" spans="1:25">
+      <c r="A12" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="5">
+        <v>39992.32</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="7">
+        <v>39992.32</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="9">
+        <v>2</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="9">
+        <v>40</v>
+      </c>
+      <c r="K12" s="9">
+        <v>640</v>
+      </c>
+      <c r="L12" s="10">
+        <v>10240</v>
+      </c>
+      <c r="M12" s="10">
+        <v>10240</v>
+      </c>
+      <c r="N12" s="11">
+        <v>10956.8</v>
+      </c>
+      <c r="O12" s="11">
+        <v>13200</v>
+      </c>
+      <c r="P12" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="V12" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="W12" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+    </row>
+    <row r="13" ht="15" spans="1:25">
+      <c r="A13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="5">
+        <v>279946.24</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="7">
+        <v>279946.24</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="9">
+        <v>14</v>
+      </c>
+      <c r="H13" s="9">
+        <v>7</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" s="9">
+        <v>280</v>
+      </c>
+      <c r="K13" s="10">
+        <v>4480</v>
+      </c>
+      <c r="L13" s="10">
+        <v>71680</v>
+      </c>
+      <c r="M13" s="10">
+        <v>71680</v>
+      </c>
+      <c r="N13" s="11">
+        <v>76697.6</v>
+      </c>
+      <c r="O13" s="11">
+        <v>92400</v>
+      </c>
+      <c r="P13" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="U13" s="14">
+        <v>46153</v>
+      </c>
+      <c r="V13" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="W13" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+    </row>
+    <row r="14" ht="15" spans="1:25">
+      <c r="A14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="5">
+        <v>279946.24</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="7">
+        <v>279946.24</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="9">
+        <v>14</v>
+      </c>
+      <c r="H14" s="9">
+        <v>7</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J14" s="9">
+        <v>280</v>
+      </c>
+      <c r="K14" s="10">
+        <v>4480</v>
+      </c>
+      <c r="L14" s="10">
+        <v>71680</v>
+      </c>
+      <c r="M14" s="10">
+        <v>71680</v>
+      </c>
+      <c r="N14" s="11">
+        <v>76697.6</v>
+      </c>
+      <c r="O14" s="11">
+        <v>92400</v>
+      </c>
+      <c r="P14" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="U14" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="V14" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="W14" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+    </row>
+    <row r="15" ht="15" spans="1:25">
+      <c r="A15" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="16">
+        <v>279946.24</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="18">
+        <v>279946.24</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="9">
+        <v>14</v>
+      </c>
+      <c r="H15" s="9">
+        <v>7</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="9">
+        <v>280</v>
+      </c>
+      <c r="K15" s="10">
+        <v>4480</v>
+      </c>
+      <c r="L15" s="10">
+        <v>71680</v>
+      </c>
+      <c r="M15" s="10">
+        <v>71680</v>
+      </c>
+      <c r="N15" s="11">
+        <v>76697.6</v>
+      </c>
+      <c r="O15" s="11">
+        <v>92400</v>
+      </c>
+      <c r="P15" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="U15" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="V15" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="W15" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+    </row>
+    <row r="16" ht="15" spans="1:25">
+      <c r="A16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="21">
+        <v>119976.96</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="12">
+        <v>119976.96</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="9">
         <v>6</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="H16" s="9">
+        <v>3</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="9">
         <v>120</v>
       </c>
-      <c r="H3" s="5">
-        <v>2400</v>
-      </c>
-      <c r="I3" s="5">
-        <v>57600</v>
-      </c>
-      <c r="J3" s="5">
-        <v>57600</v>
-      </c>
-      <c r="K3" s="6">
-        <v>72720</v>
-      </c>
-      <c r="L3" s="6">
-        <v>79200</v>
-      </c>
-      <c r="M3" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="N3" s="7">
-        <v>270720</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3" s="4" t="s">
+      <c r="K16" s="10">
+        <v>1920</v>
+      </c>
+      <c r="L16" s="10">
+        <v>30720</v>
+      </c>
+      <c r="M16" s="10">
+        <v>30720</v>
+      </c>
+      <c r="N16" s="11">
+        <v>32870.4</v>
+      </c>
+      <c r="O16" s="11">
+        <v>39600</v>
+      </c>
+      <c r="P16" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="Q16" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="S3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="R16" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="U16" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="V16" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="W16" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
     </row>
-    <row r="4" ht="14.25" spans="1:20">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="3">
-        <v>161571.57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="4">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4">
-        <v>4</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="4">
-        <v>158</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2528</v>
-      </c>
-      <c r="I4" s="5">
-        <v>41312</v>
-      </c>
-      <c r="J4" s="5">
-        <v>40448</v>
-      </c>
-      <c r="K4" s="6">
-        <v>42188.8</v>
-      </c>
-      <c r="L4" s="6">
-        <v>52140</v>
-      </c>
-      <c r="M4" s="7">
+    <row r="17" ht="15" spans="1:25">
+      <c r="A17" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="21">
+        <v>279946.24</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="12">
+        <v>279946.24</v>
+      </c>
+      <c r="E17" s="12"/>
+      <c r="F17" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="9">
+        <v>14</v>
+      </c>
+      <c r="H17" s="9">
+        <v>7</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="9">
+        <v>280</v>
+      </c>
+      <c r="K17" s="10">
+        <v>4480</v>
+      </c>
+      <c r="L17" s="10">
+        <v>71680</v>
+      </c>
+      <c r="M17" s="10">
+        <v>71680</v>
+      </c>
+      <c r="N17" s="11">
+        <v>76697.6</v>
+      </c>
+      <c r="O17" s="11">
+        <v>92400</v>
+      </c>
+      <c r="P17" s="12">
         <v>4.6</v>
       </c>
-      <c r="N4" s="7">
-        <v>186060.8</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q17" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="S17" s="14">
+        <v>46182</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="U17" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="V17" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="W17" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
     </row>
-    <row r="5" ht="14.25" spans="1:20">
-      <c r="A5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="3">
-        <v>239953.92</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="4">
-        <v>12</v>
-      </c>
-      <c r="E5" s="4">
-        <v>6</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="4">
-        <v>240</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3840</v>
-      </c>
-      <c r="I5" s="5">
-        <v>61440</v>
-      </c>
-      <c r="J5" s="5">
-        <v>61440</v>
-      </c>
-      <c r="K5" s="6">
-        <v>65740.8</v>
-      </c>
-      <c r="L5" s="6">
-        <v>79200</v>
-      </c>
-      <c r="M5" s="7">
+    <row r="18" ht="15" spans="1:25">
+      <c r="A18" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="22">
+        <v>279946.24</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="23">
+        <v>279946.24</v>
+      </c>
+      <c r="E18" s="23"/>
+      <c r="F18" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="6">
+        <v>14</v>
+      </c>
+      <c r="H18" s="6">
+        <v>7</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="6">
+        <v>280</v>
+      </c>
+      <c r="K18" s="24">
+        <v>4480</v>
+      </c>
+      <c r="L18" s="24">
+        <v>71680</v>
+      </c>
+      <c r="M18" s="24">
+        <v>71680</v>
+      </c>
+      <c r="N18" s="25">
+        <v>76697.6</v>
+      </c>
+      <c r="O18" s="25">
+        <v>92400</v>
+      </c>
+      <c r="P18" s="12">
         <v>4.6</v>
       </c>
-      <c r="N5" s="7">
-        <v>282624</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="Q18" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="S18" s="14">
+        <v>46189</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="U18" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="V18" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="W18" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
     </row>
-    <row r="6" ht="14.25" spans="1:20">
-      <c r="A6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="3">
-        <v>199961.6</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="4">
-        <v>10</v>
-      </c>
-      <c r="E6" s="4">
-        <v>5</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="4">
-        <v>200</v>
-      </c>
-      <c r="H6" s="5">
-        <v>3200</v>
-      </c>
-      <c r="I6" s="5">
-        <v>51200</v>
-      </c>
-      <c r="J6" s="5">
-        <v>51200</v>
-      </c>
-      <c r="K6" s="6">
-        <v>54784</v>
-      </c>
-      <c r="L6" s="6">
-        <v>66000</v>
-      </c>
-      <c r="M6" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N6" s="7">
-        <v>235520</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="R6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
-      <c r="A7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="3">
-        <v>99980.8</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="4">
-        <v>5</v>
-      </c>
-      <c r="E7" s="4">
-        <v>3</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="4">
-        <v>100</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1600</v>
-      </c>
-      <c r="I7" s="5">
-        <v>25600</v>
-      </c>
-      <c r="J7" s="5">
-        <v>25600</v>
-      </c>
-      <c r="K7" s="6">
-        <v>27392</v>
-      </c>
-      <c r="L7" s="6">
-        <v>33000</v>
-      </c>
-      <c r="M7" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N7" s="7">
-        <v>117760</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" spans="1:20">
-      <c r="A8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="3">
-        <v>139973.12</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="4">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4">
-        <v>4</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="4">
-        <v>140</v>
-      </c>
-      <c r="H8" s="5">
-        <v>2240</v>
-      </c>
-      <c r="I8" s="5">
-        <v>35840</v>
-      </c>
-      <c r="J8" s="5">
-        <v>35840</v>
-      </c>
-      <c r="K8" s="6">
-        <v>38348.8</v>
-      </c>
-      <c r="L8" s="6">
-        <v>46200</v>
-      </c>
-      <c r="M8" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N8" s="7">
-        <v>164864</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="1:20">
-      <c r="A9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="3">
-        <v>99980.8</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="4">
-        <v>5</v>
-      </c>
-      <c r="E9" s="4">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="4">
-        <v>100</v>
-      </c>
-      <c r="H9" s="5">
-        <v>1600</v>
-      </c>
-      <c r="I9" s="5">
-        <v>25600</v>
-      </c>
-      <c r="J9" s="5">
-        <v>25600</v>
-      </c>
-      <c r="K9" s="6">
-        <v>27392</v>
-      </c>
-      <c r="L9" s="6">
-        <v>33000</v>
-      </c>
-      <c r="M9" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N9" s="7">
-        <v>117760</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T9" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" spans="1:20">
-      <c r="A10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="3">
-        <v>139973.12</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="4">
-        <v>7</v>
-      </c>
-      <c r="E10" s="4">
-        <v>4</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="4">
-        <v>140</v>
-      </c>
-      <c r="H10" s="5">
-        <v>2240</v>
-      </c>
-      <c r="I10" s="5">
-        <v>35840</v>
-      </c>
-      <c r="J10" s="5">
-        <v>35840</v>
-      </c>
-      <c r="K10" s="6">
-        <v>38348.8</v>
-      </c>
-      <c r="L10" s="6">
-        <v>46200</v>
-      </c>
-      <c r="M10" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N10" s="7">
-        <v>164864</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="T10" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="1:20">
-      <c r="A11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="3">
-        <v>159969.28</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="4">
-        <v>8</v>
-      </c>
-      <c r="E11" s="4">
-        <v>4</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="4">
-        <v>160</v>
-      </c>
-      <c r="H11" s="5">
-        <v>2560</v>
-      </c>
-      <c r="I11" s="5">
-        <v>40960</v>
-      </c>
-      <c r="J11" s="5">
-        <v>40960</v>
-      </c>
-      <c r="K11" s="6">
-        <v>43827.2</v>
-      </c>
-      <c r="L11" s="6">
-        <v>52800</v>
-      </c>
-      <c r="M11" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N11" s="7">
-        <v>188416</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="R11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="T11" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" spans="1:20">
-      <c r="A12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="3">
-        <v>39992.32</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="4">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="4">
-        <v>40</v>
-      </c>
-      <c r="H12" s="4">
-        <v>640</v>
-      </c>
-      <c r="I12" s="5">
-        <v>10240</v>
-      </c>
-      <c r="J12" s="5">
-        <v>10240</v>
-      </c>
-      <c r="K12" s="6">
-        <v>10956.8</v>
-      </c>
-      <c r="L12" s="6">
-        <v>13200</v>
-      </c>
-      <c r="M12" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N12" s="7">
-        <v>47104</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="T12" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:20">
-      <c r="A13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="3">
-        <v>279946.24</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="4">
-        <v>14</v>
-      </c>
-      <c r="E13" s="4">
-        <v>7</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="4">
-        <v>280</v>
-      </c>
-      <c r="H13" s="5">
-        <v>4480</v>
-      </c>
-      <c r="I13" s="5">
-        <v>71680</v>
-      </c>
-      <c r="J13" s="5">
-        <v>71680</v>
-      </c>
-      <c r="K13" s="6">
-        <v>76697.6</v>
-      </c>
-      <c r="L13" s="6">
-        <v>92400</v>
-      </c>
-      <c r="M13" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N13" s="7">
-        <v>329728</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="R13" s="9">
-        <v>46153</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="T13" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" spans="1:20">
-      <c r="A14" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" s="3">
-        <v>279946.24</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="4">
-        <v>14</v>
-      </c>
-      <c r="E14" s="4">
-        <v>7</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="4">
-        <v>280</v>
-      </c>
-      <c r="H14" s="5">
-        <v>4480</v>
-      </c>
-      <c r="I14" s="5">
-        <v>71680</v>
-      </c>
-      <c r="J14" s="5">
-        <v>71680</v>
-      </c>
-      <c r="K14" s="6">
-        <v>76697.6</v>
-      </c>
-      <c r="L14" s="6">
-        <v>92400</v>
-      </c>
-      <c r="M14" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N14" s="7">
-        <v>329728</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T14" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="1:20">
-      <c r="A15" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="11">
-        <v>279946.24</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="4">
-        <v>14</v>
-      </c>
-      <c r="E15" s="4">
-        <v>7</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="4">
-        <v>280</v>
-      </c>
-      <c r="H15" s="5">
-        <v>4480</v>
-      </c>
-      <c r="I15" s="5">
-        <v>71680</v>
-      </c>
-      <c r="J15" s="5">
-        <v>71680</v>
-      </c>
-      <c r="K15" s="6">
-        <v>76697.6</v>
-      </c>
-      <c r="L15" s="6">
-        <v>92400</v>
-      </c>
-      <c r="M15" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N15" s="7">
-        <v>329728</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T15" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" spans="1:20">
-      <c r="A16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="7">
-        <v>119976.96</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="4">
-        <v>6</v>
-      </c>
-      <c r="E16" s="4">
-        <v>3</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="4">
-        <v>120</v>
-      </c>
-      <c r="H16" s="5">
-        <v>1920</v>
-      </c>
-      <c r="I16" s="5">
-        <v>30720</v>
-      </c>
-      <c r="J16" s="5">
-        <v>30720</v>
-      </c>
-      <c r="K16" s="6">
-        <v>32870.4</v>
-      </c>
-      <c r="L16" s="6">
-        <v>39600</v>
-      </c>
-      <c r="M16" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N16" s="7">
-        <v>141312</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="R16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T16" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="1:20">
-      <c r="A17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B17" s="7">
-        <v>279946.24</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="4">
-        <v>14</v>
-      </c>
-      <c r="E17" s="4">
-        <v>7</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="4">
-        <v>280</v>
-      </c>
-      <c r="H17" s="5">
-        <v>4480</v>
-      </c>
-      <c r="I17" s="5">
-        <v>71680</v>
-      </c>
-      <c r="J17" s="5">
-        <v>71680</v>
-      </c>
-      <c r="K17" s="6">
-        <v>76697.6</v>
-      </c>
-      <c r="L17" s="6">
-        <v>92400</v>
-      </c>
-      <c r="M17" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N17" s="7">
-        <v>329728</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="P17" s="9">
-        <v>46182</v>
-      </c>
-      <c r="Q17" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="R17" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S17" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T17" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" spans="1:20">
-      <c r="A18" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" s="13">
-        <v>279946.24</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="2">
-        <v>14</v>
-      </c>
-      <c r="E18" s="2">
-        <v>7</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="2">
-        <v>280</v>
-      </c>
-      <c r="H18" s="14">
-        <v>4480</v>
-      </c>
-      <c r="I18" s="14">
-        <v>71680</v>
-      </c>
-      <c r="J18" s="14">
-        <v>71680</v>
-      </c>
-      <c r="K18" s="15">
-        <v>76697.6</v>
-      </c>
-      <c r="L18" s="15">
-        <v>92400</v>
-      </c>
-      <c r="M18" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="N18" s="13">
-        <v>329728</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="P18" s="9">
-        <v>46189</v>
-      </c>
-      <c r="Q18" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="R18" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="1:20">
-      <c r="A19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="13">
+    <row r="19" ht="15" spans="1:25">
+      <c r="A19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="22">
         <v>3441000.69</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G19" s="14">
+      <c r="C19" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="23">
+        <v>3441000.69</v>
+      </c>
+      <c r="E19" s="23"/>
+      <c r="F19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="24">
         <v>3118</v>
       </c>
-      <c r="H19" s="14">
+      <c r="K19" s="24">
         <v>51168</v>
       </c>
-      <c r="I19" s="14">
+      <c r="L19" s="24">
         <v>870752</v>
       </c>
-      <c r="J19" s="14">
+      <c r="M19" s="24">
         <v>869888</v>
       </c>
-      <c r="K19" s="15">
+      <c r="N19" s="25">
         <v>959257.6</v>
       </c>
-      <c r="L19" s="15">
+      <c r="O19" s="25">
         <v>1134540</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="N19" s="13">
-        <v>4016844.8</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>113</v>
-      </c>
+      <c r="P19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q19" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="S19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="T19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="U19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="V19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="W19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/lot-details.xlsx
+++ b/data/lot-details.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="139">
   <si>
     <t>进口批次 / 货品</t>
   </si>
@@ -36,6 +36,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -126,6 +133,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 1</t>
     </r>
     <r>
@@ -140,6 +154,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
       <t>yes</t>
     </r>
     <r>
@@ -159,9 +179,6 @@
     <t>单层平铺 (20托)</t>
   </si>
   <si>
-    <t>#########</t>
-  </si>
-  <si>
     <t>1月26日</t>
   </si>
   <si>
@@ -202,6 +219,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 2</t>
     </r>
     <r>
@@ -243,6 +267,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 3</t>
     </r>
     <r>
@@ -299,6 +330,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 4</t>
     </r>
     <r>
@@ -358,6 +396,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 5</t>
     </r>
     <r>
@@ -411,6 +456,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 6</t>
     </r>
     <r>
@@ -464,6 +516,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 7</t>
     </r>
     <r>
@@ -523,6 +582,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 8</t>
     </r>
     <r>
@@ -570,6 +636,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 9</t>
     </r>
     <r>
@@ -611,6 +684,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 10.1</t>
     </r>
     <r>
@@ -658,6 +738,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 10.2</t>
     </r>
     <r>
@@ -699,6 +786,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 11</t>
     </r>
     <r>
@@ -719,6 +813,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>MSK</t>
     </r>
     <r>
@@ -760,6 +860,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 12</t>
     </r>
     <r>
@@ -780,6 +887,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Cosco</t>
     </r>
     <r>
@@ -794,6 +907,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">5/18/2026 </t>
     </r>
     <r>
@@ -832,6 +951,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 13</t>
     </r>
     <r>
@@ -876,6 +1002,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 14</t>
     </r>
     <r>
@@ -920,6 +1053,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 15</t>
     </r>
     <r>
@@ -961,6 +1101,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
       <t>Lot 16</t>
     </r>
     <r>
@@ -977,19 +1124,36 @@
     <t>新单接入(BL:269501684)</t>
   </si>
   <si>
+    <r>
+      <t>Lot 17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>新单接入(BL:269748417)</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
     <t>全局合计</t>
   </si>
   <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>156柜</t>
-  </si>
-  <si>
-    <t>88柜</t>
-  </si>
-  <si>
-    <t>省下68柜</t>
+    <t>170柜</t>
+  </si>
+  <si>
+    <t>95柜</t>
+  </si>
+  <si>
+    <t>省下75柜</t>
   </si>
 </sst>
 </file>
@@ -1718,7 +1882,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1758,6 +1922,9 @@
     <xf numFmtId="8" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1782,9 +1949,6 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="8" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1795,6 +1959,21 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -2322,16 +2501,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.75" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="15.375" customWidth="1"/>
     <col min="6" max="6" width="12.75" customWidth="1"/>
     <col min="11" max="12" width="13" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="12.125"/>
+    <col min="17" max="17" width="19.875" customWidth="1"/>
     <col min="18" max="18" width="13.625" customWidth="1"/>
     <col min="20" max="20" width="24.375" customWidth="1"/>
   </cols>
@@ -2458,39 +2639,39 @@
       <c r="P2" s="12">
         <v>4.7</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="13">
+        <v>451200</v>
+      </c>
+      <c r="R2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="S2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="T2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="U2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="W2" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="W2" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
     </row>
     <row r="3" ht="15" spans="1:25">
       <c r="A3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="5">
         <v>239976</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="7">
         <v>239976</v>
@@ -2531,39 +2712,39 @@
       <c r="P3" s="12">
         <v>4.7</v>
       </c>
-      <c r="Q3" s="12" t="s">
-        <v>26</v>
+      <c r="Q3" s="13">
+        <v>270720</v>
       </c>
       <c r="R3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="T3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="U3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="W3" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="W3" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
     </row>
     <row r="4" ht="15" spans="1:25">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="5">
         <v>161571.57</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" s="7">
         <v>161571.57</v>
@@ -2572,7 +2753,7 @@
         <v>23</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4" s="9">
         <v>8</v>
@@ -2581,7 +2762,7 @@
         <v>4</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J4" s="9">
         <v>158</v>
@@ -2604,39 +2785,39 @@
       <c r="P4" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q4" s="12" t="s">
-        <v>26</v>
+      <c r="Q4" s="13">
+        <v>186060.8</v>
       </c>
       <c r="R4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="S4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T4" s="9" t="s">
+      <c r="U4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="V4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="W4" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
     <row r="5" ht="15" spans="1:25">
       <c r="A5" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" s="5">
         <v>239953.92</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="7">
         <v>239953.92</v>
@@ -2645,7 +2826,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" s="9">
         <v>12</v>
@@ -2654,7 +2835,7 @@
         <v>6</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J5" s="9">
         <v>240</v>
@@ -2677,39 +2858,39 @@
       <c r="P5" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q5" s="12" t="s">
-        <v>26</v>
+      <c r="Q5" s="13">
+        <v>282624</v>
       </c>
       <c r="R5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="S5" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="T5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="T5" s="9" t="s">
+      <c r="U5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="U5" s="9" t="s">
+      <c r="V5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="V5" s="9" t="s">
+      <c r="W5" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="W5" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
     </row>
     <row r="6" ht="15" spans="1:25">
       <c r="A6" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5">
         <v>199961.6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6" s="7">
         <v>199961.6</v>
@@ -2718,7 +2899,7 @@
         <v>23</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6" s="9">
         <v>10</v>
@@ -2727,7 +2908,7 @@
         <v>5</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J6" s="9">
         <v>200</v>
@@ -2750,39 +2931,39 @@
       <c r="P6" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q6" s="12" t="s">
-        <v>26</v>
+      <c r="Q6" s="13">
+        <v>235520</v>
       </c>
       <c r="R6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="T6" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="T6" s="9" t="s">
+      <c r="U6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="V6" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="U6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="V6" s="9" t="s">
+      <c r="W6" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="W6" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
     </row>
     <row r="7" ht="15" spans="1:25">
       <c r="A7" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" s="5">
         <v>99980.8</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" s="7">
         <v>99980.8</v>
@@ -2791,7 +2972,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7" s="9">
         <v>5</v>
@@ -2800,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J7" s="9">
         <v>100</v>
@@ -2823,39 +3004,39 @@
       <c r="P7" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q7" s="12" t="s">
-        <v>26</v>
+      <c r="Q7" s="13">
+        <v>117760</v>
       </c>
       <c r="R7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="S7" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="S7" s="9" t="s">
+      <c r="T7" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="T7" s="9" t="s">
+      <c r="U7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="U7" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="W7" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
     </row>
     <row r="8" ht="15" spans="1:25">
       <c r="A8" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="5">
         <v>139973.12</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" s="7">
         <v>139973.12</v>
@@ -2864,7 +3045,7 @@
         <v>23</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G8" s="9">
         <v>7</v>
@@ -2873,7 +3054,7 @@
         <v>4</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J8" s="9">
         <v>140</v>
@@ -2896,39 +3077,39 @@
       <c r="P8" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q8" s="12" t="s">
-        <v>26</v>
+      <c r="Q8" s="13">
+        <v>164864</v>
       </c>
       <c r="R8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="S8" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="T8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="T8" s="9" t="s">
+      <c r="U8" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="U8" s="9" t="s">
+      <c r="V8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="V8" s="9" t="s">
+      <c r="W8" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="W8" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
     </row>
     <row r="9" ht="15" spans="1:25">
       <c r="A9" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" s="5">
         <v>99980.8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" s="7">
         <v>99980.8</v>
@@ -2937,7 +3118,7 @@
         <v>23</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G9" s="9">
         <v>5</v>
@@ -2946,7 +3127,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J9" s="9">
         <v>100</v>
@@ -2969,39 +3150,39 @@
       <c r="P9" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q9" s="12" t="s">
-        <v>26</v>
+      <c r="Q9" s="13">
+        <v>117760</v>
       </c>
       <c r="R9" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="S9" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="S9" s="9" t="s">
+      <c r="T9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="U9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W9" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="T9" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="W9" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
     <row r="10" ht="15" spans="1:25">
       <c r="A10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="5">
         <v>139973.12</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" s="7">
         <v>139973.12</v>
@@ -3009,8 +3190,8 @@
       <c r="E10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>58</v>
+      <c r="F10" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="G10" s="9">
         <v>7</v>
@@ -3019,7 +3200,7 @@
         <v>4</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J10" s="9">
         <v>140</v>
@@ -3042,39 +3223,39 @@
       <c r="P10" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q10" s="12" t="s">
-        <v>26</v>
+      <c r="Q10" s="13">
+        <v>164864</v>
       </c>
       <c r="R10" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="S10" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="S10" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="T10" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="U10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="V10" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="U10" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="V10" s="9" t="s">
+      <c r="W10" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="W10" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
     <row r="11" ht="15" spans="1:25">
       <c r="A11" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B11" s="5">
         <v>159969.28</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" s="7">
         <v>159969.28</v>
@@ -3082,8 +3263,8 @@
       <c r="E11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>94</v>
+      <c r="F11" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="G11" s="9">
         <v>8</v>
@@ -3092,7 +3273,7 @@
         <v>4</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J11" s="9">
         <v>160</v>
@@ -3115,39 +3296,39 @@
       <c r="P11" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q11" s="12" t="s">
-        <v>26</v>
+      <c r="Q11" s="13">
+        <v>188416</v>
       </c>
       <c r="R11" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S11" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="S11" s="9" t="s">
+      <c r="T11" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="T11" s="9" t="s">
-        <v>97</v>
-      </c>
       <c r="U11" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="V11" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="W11" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="W11" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="15" spans="1:25">
       <c r="A12" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" s="5">
         <v>39992.32</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D12" s="7">
         <v>39992.32</v>
@@ -3156,7 +3337,7 @@
         <v>23</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12" s="9">
         <v>2</v>
@@ -3165,7 +3346,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J12" s="9">
         <v>40</v>
@@ -3188,39 +3369,39 @@
       <c r="P12" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q12" s="12" t="s">
-        <v>26</v>
+      <c r="Q12" s="13">
+        <v>47104</v>
       </c>
       <c r="R12" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S12" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="S12" s="9" t="s">
-        <v>96</v>
-      </c>
       <c r="T12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="V12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="U12" s="9" t="s">
+      <c r="W12" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="V12" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="W12" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="15" spans="1:25">
       <c r="A13" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" s="5">
         <v>279946.24</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" s="7">
         <v>279946.24</v>
@@ -3229,7 +3410,7 @@
         <v>23</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13" s="9">
         <v>14</v>
@@ -3238,7 +3419,7 @@
         <v>7</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J13" s="9">
         <v>280</v>
@@ -3261,39 +3442,39 @@
       <c r="P13" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q13" s="12" t="s">
-        <v>26</v>
+      <c r="Q13" s="13">
+        <v>329728</v>
       </c>
       <c r="R13" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="S13" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="T13" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="T13" s="9" t="s">
+      <c r="U13" s="15">
+        <v>46153</v>
+      </c>
+      <c r="V13" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="U13" s="14">
-        <v>46153</v>
-      </c>
-      <c r="V13" s="9" t="s">
+      <c r="W13" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="W13" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="15" spans="1:25">
       <c r="A14" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B14" s="5">
         <v>279946.24</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D14" s="7">
         <v>279946.24</v>
@@ -3302,7 +3483,7 @@
         <v>23</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G14" s="9">
         <v>14</v>
@@ -3311,7 +3492,7 @@
         <v>7</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J14" s="9">
         <v>280</v>
@@ -3334,48 +3515,48 @@
       <c r="P14" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q14" s="12" t="s">
-        <v>26</v>
+      <c r="Q14" s="13">
+        <v>329728</v>
       </c>
       <c r="R14" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="S14" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="S14" s="9" t="s">
+      <c r="T14" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="T14" s="9" t="s">
+      <c r="U14" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="U14" s="14" t="s">
+      <c r="V14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W14" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="V14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="W14" s="9" t="s">
-        <v>115</v>
       </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
     <row r="15" ht="15" spans="1:25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="17">
+        <v>279946.24</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="16">
+      <c r="D15" s="19">
         <v>279946.24</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="E15" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="18">
-        <v>279946.24</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>84</v>
+      <c r="F15" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="G15" s="9">
         <v>14</v>
@@ -3384,7 +3565,7 @@
         <v>7</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15" s="9">
         <v>280</v>
@@ -3407,48 +3588,48 @@
       <c r="P15" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q15" s="12" t="s">
-        <v>26</v>
+      <c r="Q15" s="13">
+        <v>329728</v>
       </c>
       <c r="R15" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="S15" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="S15" s="9" t="s">
-        <v>120</v>
-      </c>
       <c r="T15" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="U15" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="U15" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="V15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W15" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="V15" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="W15" s="9" t="s">
-        <v>115</v>
       </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="15" spans="1:25">
       <c r="A16" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="13">
+        <v>119976.96</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="B16" s="21">
-        <v>119976.96</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="D16" s="12">
         <v>119976.96</v>
       </c>
-      <c r="E16" s="19" t="s">
-        <v>118</v>
+      <c r="E16" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G16" s="9">
         <v>6</v>
@@ -3457,7 +3638,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J16" s="9">
         <v>120</v>
@@ -3480,46 +3661,46 @@
       <c r="P16" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q16" s="12" t="s">
-        <v>26</v>
+      <c r="Q16" s="13">
+        <v>141312</v>
       </c>
       <c r="R16" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="S16" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="S16" s="9" t="s">
+      <c r="T16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="U16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="V16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W16" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="T16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="U16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="V16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="W16" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" ht="15" spans="1:25">
+    <row r="17" ht="15" spans="1:27">
       <c r="A17" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="13">
+        <v>279946.24</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="B17" s="21">
-        <v>279946.24</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="D17" s="12">
         <v>279946.24</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G17" s="9">
         <v>14</v>
@@ -3528,7 +3709,7 @@
         <v>7</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J17" s="9">
         <v>280</v>
@@ -3551,46 +3732,46 @@
       <c r="P17" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q17" s="12" t="s">
-        <v>26</v>
+      <c r="Q17" s="13">
+        <v>329728</v>
       </c>
       <c r="R17" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="S17" s="15">
+        <v>46182</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="U17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="V17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W17" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="S17" s="14">
-        <v>46182</v>
-      </c>
-      <c r="T17" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="U17" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="V17" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="W17" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" ht="15" spans="1:25">
+    <row r="18" ht="15" spans="1:27">
       <c r="A18" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B18" s="22">
         <v>279946.24</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D18" s="23">
         <v>279946.24</v>
       </c>
       <c r="E18" s="23"/>
       <c r="F18" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G18" s="6">
         <v>14</v>
@@ -3599,7 +3780,7 @@
         <v>7</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J18" s="6">
         <v>280</v>
@@ -3622,100 +3803,169 @@
       <c r="P18" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q18" s="23" t="s">
-        <v>26</v>
+      <c r="Q18" s="22">
+        <v>329728</v>
       </c>
       <c r="R18" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="S18" s="14">
+        <v>127</v>
+      </c>
+      <c r="S18" s="15">
         <v>46189</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W18" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" ht="15" spans="1:25">
-      <c r="A19" s="4" t="s">
+    <row r="19" ht="15" spans="1:27">
+      <c r="A19" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="27">
+        <v>279946.24</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="27">
+        <v>279946.24</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="26">
+        <v>14</v>
+      </c>
+      <c r="H19" s="26">
+        <v>7</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" s="26">
+        <v>280</v>
+      </c>
+      <c r="K19" s="29">
+        <v>4480</v>
+      </c>
+      <c r="L19" s="29">
+        <v>71680</v>
+      </c>
+      <c r="M19" s="29">
+        <v>71680</v>
+      </c>
+      <c r="N19" s="30">
+        <v>76697.6</v>
+      </c>
+      <c r="O19" s="30">
+        <v>92400</v>
+      </c>
+      <c r="P19" s="27">
+        <v>4.6</v>
+      </c>
+      <c r="Q19" s="27">
+        <v>329728</v>
+      </c>
+      <c r="R19" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="S19" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="T19" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="U19" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="V19" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="W19" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="22">
-        <v>3441000.69</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" s="23">
-        <v>3441000.69</v>
-      </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="6" t="s">
+      <c r="X19" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="Y19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" ht="14.25" spans="1:27">
+      <c r="A20" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="B20" s="27">
+        <v>3720946.93</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="G20" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="H20" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="J19" s="24">
-        <v>3118</v>
-      </c>
-      <c r="K19" s="24">
-        <v>51168</v>
-      </c>
-      <c r="L19" s="24">
-        <v>870752</v>
-      </c>
-      <c r="M19" s="24">
-        <v>869888</v>
-      </c>
-      <c r="N19" s="25">
-        <v>959257.6</v>
-      </c>
-      <c r="O19" s="25">
-        <v>1134540</v>
-      </c>
-      <c r="P19" s="6" t="s">
+      <c r="I20" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="J20" s="29">
+        <v>3398</v>
+      </c>
+      <c r="K20" s="29">
+        <v>55648</v>
+      </c>
+      <c r="L20" s="29">
+        <v>942432</v>
+      </c>
+      <c r="M20" s="29">
+        <v>941568</v>
+      </c>
+      <c r="N20" s="30">
+        <v>1035955.2</v>
+      </c>
+      <c r="O20" s="30">
+        <v>1226940</v>
+      </c>
+      <c r="P20" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="Q19" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="R19" s="6" t="s">
+      <c r="Q20" s="27">
+        <v>4346572.8</v>
+      </c>
+      <c r="R20" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="S19" s="6" t="s">
+      <c r="S20" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="T19" s="6" t="s">
+      <c r="T20" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="U19" s="6" t="s">
+      <c r="U20" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="V19" s="6" t="s">
+      <c r="V20" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="W19" s="6" t="s">
+      <c r="W20" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/lot-details.xlsx
+++ b/data/lot-details.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="137">
   <si>
     <t>进口批次 / 货品</t>
   </si>
@@ -305,7 +305,7 @@
     <t>4月27日</t>
   </si>
   <si>
-    <t>二程严重延误 10 天</t>
+    <t>已抵上海</t>
   </si>
   <si>
     <r>
@@ -371,9 +371,6 @@
     <t>4月26日</t>
   </si>
   <si>
-    <t>已抵上海</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -431,9 +428,6 @@
     <t>5月11日</t>
   </si>
   <si>
-    <t>二程在途 (合并装运)</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -491,9 +485,6 @@
     <t>待定</t>
   </si>
   <si>
-    <t>头程严重延误 17 天</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -557,9 +548,6 @@
     <t>5月3日</t>
   </si>
   <si>
-    <t>二程在途 (早于Lot5发运)</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -602,16 +590,481 @@
     </r>
   </si>
   <si>
+    <t>Export lot 10</t>
+  </si>
+  <si>
+    <t>3月5日</t>
+  </si>
+  <si>
+    <t>5月20日</t>
+  </si>
+  <si>
+    <t>已经订舱</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lot 9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Lot 9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>3月1日</t>
+  </si>
+  <si>
+    <t>4月16日</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lot 10.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Lot 10.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>Export Lot 6</t>
+  </si>
+  <si>
+    <t>3月8日</t>
+  </si>
+  <si>
+    <t>4月21日</t>
+  </si>
+  <si>
+    <t>EVER LUNAR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lot 10.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Lot 10.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>5月1日</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lot 11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Lot 11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>3月16日</t>
+  </si>
+  <si>
+    <t>4月28日</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>MSK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>5月17日</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lot 12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Lot 12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>Export lot 8</t>
+  </si>
+  <si>
+    <t>3月22日</t>
+  </si>
+  <si>
+    <t>5月9日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSK </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">5/18/2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="SimSun"/>
+        <charset val="0"/>
+      </rPr>
+      <t>暂定</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lot 13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Lot 13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>estimate 5/20</t>
+  </si>
+  <si>
+    <t>Export lot 9</t>
+  </si>
+  <si>
+    <t>3月29日</t>
+  </si>
+  <si>
+    <t>5月12日</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="SimSun"/>
+        <charset val="0"/>
+      </rPr>
+      <t>在途</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lot 14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Lot 14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <t>Export Lot 10</t>
+  </si>
+  <si>
+    <t>4月9日</t>
+  </si>
+  <si>
+    <t>5月26日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSSCO </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lot 15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF303030"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Lot 15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="1rem / 1.5rem google sans text"/>
+        <charset val="0"/>
+      </rPr>
+      <t>&lt;br&gt;电池电芯</t>
+    </r>
+  </si>
+  <si>
     <t>待定 (TBD)</t>
   </si>
   <si>
-    <t>3月5日</t>
-  </si>
-  <si>
-    <t>5月20日</t>
-  </si>
-  <si>
-    <t>头程极度延误 32 天</t>
+    <t>待确认</t>
+  </si>
+  <si>
+    <t>上游排期待跟进</t>
   </si>
   <si>
     <r>
@@ -622,7 +1075,7 @@
         <rFont val="1rem / 1.5rem google sans text"/>
         <charset val="134"/>
       </rPr>
-      <t>Lot 9</t>
+      <t>Lot 16</t>
     </r>
     <r>
       <rPr>
@@ -643,7 +1096,7 @@
         <rFont val="1rem / 1.5rem google sans text"/>
         <charset val="0"/>
       </rPr>
-      <t>Lot 9</t>
+      <t>Lot 16</t>
     </r>
     <r>
       <rPr>
@@ -656,10 +1109,7 @@
     </r>
   </si>
   <si>
-    <t>3月1日</t>
-  </si>
-  <si>
-    <t>4月16日</t>
+    <t>新单接入(BL:269501684)</t>
   </si>
   <si>
     <r>
@@ -670,461 +1120,6 @@
         <rFont val="1rem / 1.5rem google sans text"/>
         <charset val="134"/>
       </rPr>
-      <t>Lot 10.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>Lot 10.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <t>Export Lot 6</t>
-  </si>
-  <si>
-    <t>3月8日</t>
-  </si>
-  <si>
-    <t>4月21日</t>
-  </si>
-  <si>
-    <t>EVER LUNAR</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Lot 10.2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>Lot 10.2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <t>5月1日</t>
-  </si>
-  <si>
-    <t>二程排期锁定</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Lot 11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>Lot 11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <t>3月16日</t>
-  </si>
-  <si>
-    <t>4月28日</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>MSK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>5月17日</t>
-  </si>
-  <si>
-    <t>头程抵达，二程锁定</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Lot 12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>Lot 12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <t>3月22日</t>
-  </si>
-  <si>
-    <t>5月9日</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>Cosco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">5/18/2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="SimSun"/>
-        <charset val="0"/>
-      </rPr>
-      <t>暂定</t>
-    </r>
-  </si>
-  <si>
-    <t>正常在途</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Lot 13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>Lot 13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <t>estimate 5/20</t>
-  </si>
-  <si>
-    <t>3月29日</t>
-  </si>
-  <si>
-    <t>5月12日</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Lot 14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>Lot 14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <t>4月9日</t>
-  </si>
-  <si>
-    <t>5月26日</t>
-  </si>
-  <si>
-    <t>头程延误 2 天</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Lot 15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>Lot 15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <t>待确认</t>
-  </si>
-  <si>
-    <t>上游排期待跟进</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Lot 16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF303030"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>Lot 16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="1rem / 1.5rem google sans text"/>
-        <charset val="0"/>
-      </rPr>
-      <t>&lt;br&gt;电池电芯</t>
-    </r>
-  </si>
-  <si>
-    <t>新单接入(BL:269501684)</t>
-  </si>
-  <si>
-    <r>
       <t>Lot 17</t>
     </r>
     <r>
@@ -1212,6 +1207,12 @@
       <sz val="10.5"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF333333"/>
+      <name val="SimSun"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1357,12 +1358,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF333333"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
     </font>
     <font>
       <b/>
@@ -1752,137 +1747,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1925,12 +1920,15 @@
     <xf numFmtId="8" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="16" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1959,12 +1957,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2500,7 +2492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -2877,20 +2869,20 @@
         <v>53</v>
       </c>
       <c r="W5" s="9" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
     </row>
     <row r="6" ht="15" spans="1:25">
       <c r="A6" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" s="5">
         <v>199961.6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" s="7">
         <v>199961.6</v>
@@ -2899,7 +2891,7 @@
         <v>23</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6" s="9">
         <v>10</v>
@@ -2935,35 +2927,35 @@
         <v>235520</v>
       </c>
       <c r="R6" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="S6" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="T6" s="9" t="s">
         <v>59</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>60</v>
       </c>
       <c r="U6" s="9" t="s">
         <v>53</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W6" s="9" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
     </row>
     <row r="7" ht="15" spans="1:25">
       <c r="A7" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B7" s="5">
         <v>99980.8</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D7" s="7">
         <v>99980.8</v>
@@ -2972,7 +2964,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G7" s="9">
         <v>5</v>
@@ -2981,7 +2973,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J7" s="9">
         <v>100</v>
@@ -3008,35 +3000,35 @@
         <v>117760</v>
       </c>
       <c r="R7" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="T7" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="S7" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U7" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>69</v>
+      <c r="U7" s="14">
+        <v>46153</v>
+      </c>
+      <c r="V7" s="14">
+        <v>46159</v>
       </c>
       <c r="W7" s="9" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
     </row>
     <row r="8" ht="15" spans="1:25">
       <c r="A8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B8" s="5">
         <v>139973.12</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D8" s="7">
         <v>139973.12</v>
@@ -3045,7 +3037,7 @@
         <v>23</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G8" s="9">
         <v>7</v>
@@ -3054,7 +3046,7 @@
         <v>4</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J8" s="9">
         <v>140</v>
@@ -3081,35 +3073,35 @@
         <v>164864</v>
       </c>
       <c r="R8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U8" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="V8" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="T8" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="U8" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="W8" s="9" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
     </row>
     <row r="9" ht="15" spans="1:25">
       <c r="A9" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B9" s="5">
         <v>99980.8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D9" s="7">
         <v>99980.8</v>
@@ -3118,7 +3110,7 @@
         <v>23</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G9" s="9">
         <v>5</v>
@@ -3127,7 +3119,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J9" s="9">
         <v>100</v>
@@ -3154,35 +3146,35 @@
         <v>117760</v>
       </c>
       <c r="R9" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="W9" s="9" t="s">
-        <v>86</v>
+        <v>67</v>
+      </c>
+      <c r="U9" s="14">
+        <v>46182</v>
+      </c>
+      <c r="V9" s="14">
+        <v>46192</v>
+      </c>
+      <c r="W9" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
     <row r="10" ht="15" spans="1:25">
       <c r="A10" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B10" s="5">
         <v>139973.12</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D10" s="7">
         <v>139973.12</v>
@@ -3190,8 +3182,8 @@
       <c r="E10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>57</v>
+      <c r="F10" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="G10" s="9">
         <v>7</v>
@@ -3200,7 +3192,7 @@
         <v>4</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J10" s="9">
         <v>140</v>
@@ -3227,35 +3219,35 @@
         <v>164864</v>
       </c>
       <c r="R10" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U10" s="9" t="s">
         <v>53</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W10" s="9" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
     <row r="11" ht="15" spans="1:25">
       <c r="A11" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B11" s="5">
         <v>159969.28</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D11" s="7">
         <v>159969.28</v>
@@ -3263,8 +3255,8 @@
       <c r="E11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>93</v>
+      <c r="F11" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="G11" s="9">
         <v>8</v>
@@ -3300,35 +3292,35 @@
         <v>188416</v>
       </c>
       <c r="R11" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="U11" s="9" t="s">
         <v>53</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="15" spans="1:25">
       <c r="A12" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B12" s="5">
         <v>39992.32</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D12" s="7">
         <v>39992.32</v>
@@ -3337,7 +3329,7 @@
         <v>23</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12" s="9">
         <v>2</v>
@@ -3373,35 +3365,35 @@
         <v>47104</v>
       </c>
       <c r="R12" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="S12" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="U12" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="T12" s="9" t="s">
+      <c r="V12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="U12" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="V12" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="W12" s="9" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="15" spans="1:25">
       <c r="A13" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B13" s="5">
         <v>279946.24</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D13" s="7">
         <v>279946.24</v>
@@ -3410,7 +3402,7 @@
         <v>23</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G13" s="9">
         <v>14</v>
@@ -3446,35 +3438,35 @@
         <v>329728</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="U13" s="15">
+        <v>100</v>
+      </c>
+      <c r="U13" s="14">
         <v>46153</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="W13" s="9" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="15" spans="1:25">
       <c r="A14" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B14" s="5">
         <v>279946.24</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D14" s="7">
         <v>279946.24</v>
@@ -3483,7 +3475,7 @@
         <v>23</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="G14" s="9">
         <v>14</v>
@@ -3519,44 +3511,44 @@
         <v>329728</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="U14" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="V14" s="9" t="s">
-        <v>69</v>
+        <v>107</v>
+      </c>
+      <c r="U14" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="V14" s="14">
+        <v>46170</v>
       </c>
       <c r="W14" s="9" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
     <row r="15" ht="15" spans="1:25">
-      <c r="A15" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" s="17">
+      <c r="A15" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="18">
         <v>279946.24</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" s="19">
+      <c r="C15" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="20">
         <v>279946.24</v>
       </c>
-      <c r="E15" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>83</v>
+      <c r="E15" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>112</v>
       </c>
       <c r="G15" s="9">
         <v>14</v>
@@ -3592,44 +3584,44 @@
         <v>329728</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U15" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="V15" s="9" t="s">
-        <v>69</v>
+        <v>107</v>
+      </c>
+      <c r="U15" s="14">
+        <v>46167</v>
+      </c>
+      <c r="V15" s="14">
+        <v>46175</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="15" spans="1:25">
       <c r="A16" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B16" s="13">
         <v>119976.96</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D16" s="12">
         <v>119976.96</v>
       </c>
-      <c r="E16" s="20" t="s">
-        <v>117</v>
+      <c r="E16" s="21" t="s">
+        <v>111</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="G16" s="9">
         <v>6</v>
@@ -3665,42 +3657,42 @@
         <v>141312</v>
       </c>
       <c r="R16" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="V16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="W16" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
+      </c>
+      <c r="U16" s="14">
+        <v>46182</v>
+      </c>
+      <c r="V16" s="14">
+        <v>46192</v>
+      </c>
+      <c r="W16" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
     <row r="17" ht="15" spans="1:27">
       <c r="A17" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B17" s="13">
         <v>279946.24</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D17" s="12">
         <v>279946.24</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="9" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="G17" s="9">
         <v>14</v>
@@ -3736,42 +3728,42 @@
         <v>329728</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="S17" s="15">
+        <v>125</v>
+      </c>
+      <c r="S17" s="14">
         <v>46182</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V17" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="W17" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
     <row r="18" ht="15" spans="1:27">
       <c r="A18" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B18" s="22">
+        <v>127</v>
+      </c>
+      <c r="B18" s="23">
         <v>279946.24</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" s="23">
+        <v>128</v>
+      </c>
+      <c r="D18" s="24">
         <v>279946.24</v>
       </c>
-      <c r="E18" s="23"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="9" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="G18" s="6">
         <v>14</v>
@@ -3785,186 +3777,186 @@
       <c r="J18" s="6">
         <v>280</v>
       </c>
-      <c r="K18" s="24">
+      <c r="K18" s="25">
         <v>4480</v>
       </c>
-      <c r="L18" s="24">
+      <c r="L18" s="25">
         <v>71680</v>
       </c>
-      <c r="M18" s="24">
+      <c r="M18" s="25">
         <v>71680</v>
       </c>
-      <c r="N18" s="25">
+      <c r="N18" s="26">
         <v>76697.6</v>
       </c>
-      <c r="O18" s="25">
+      <c r="O18" s="26">
         <v>92400</v>
       </c>
       <c r="P18" s="12">
         <v>4.6</v>
       </c>
-      <c r="Q18" s="22">
+      <c r="Q18" s="23">
         <v>329728</v>
       </c>
       <c r="R18" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="S18" s="15">
+        <v>125</v>
+      </c>
+      <c r="S18" s="14">
         <v>46189</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="W18" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
     <row r="19" ht="15" spans="1:27">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="23">
+        <v>279946.24</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="23">
+        <v>279946.24</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="4">
+        <v>14</v>
+      </c>
+      <c r="H19" s="4">
+        <v>7</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" s="4">
+        <v>280</v>
+      </c>
+      <c r="K19" s="28">
+        <v>4480</v>
+      </c>
+      <c r="L19" s="28">
+        <v>71680</v>
+      </c>
+      <c r="M19" s="28">
+        <v>71680</v>
+      </c>
+      <c r="N19" s="29">
+        <v>76697.6</v>
+      </c>
+      <c r="O19" s="29">
+        <v>92400</v>
+      </c>
+      <c r="P19" s="23">
+        <v>4.6</v>
+      </c>
+      <c r="Q19" s="23">
+        <v>329728</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="S19" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="T19" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="U19" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="V19" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="X19" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="27">
-        <v>279946.24</v>
-      </c>
-      <c r="C19" s="26" t="s">
+      <c r="Y19" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D19" s="27">
-        <v>279946.24</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="26">
-        <v>14</v>
-      </c>
-      <c r="H19" s="26">
-        <v>7</v>
-      </c>
-      <c r="I19" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="J19" s="26">
-        <v>280</v>
-      </c>
-      <c r="K19" s="29">
-        <v>4480</v>
-      </c>
-      <c r="L19" s="29">
-        <v>71680</v>
-      </c>
-      <c r="M19" s="29">
-        <v>71680</v>
-      </c>
-      <c r="N19" s="30">
-        <v>76697.6</v>
-      </c>
-      <c r="O19" s="30">
-        <v>92400</v>
-      </c>
-      <c r="P19" s="27">
-        <v>4.6</v>
-      </c>
-      <c r="Q19" s="27">
-        <v>329728</v>
-      </c>
-      <c r="R19" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="S19" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="T19" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="U19" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="V19" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="W19" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="X19" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y19" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="Z19" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AA19" s="3"/>
     </row>
     <row r="20" ht="14.25" spans="1:27">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="23">
+        <v>3720946.93</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="27">
-        <v>3720946.93</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="G20" s="26" t="s">
+      <c r="I20" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="H20" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="J20" s="29">
+      <c r="J20" s="28">
         <v>3398</v>
       </c>
-      <c r="K20" s="29">
+      <c r="K20" s="28">
         <v>55648</v>
       </c>
-      <c r="L20" s="29">
+      <c r="L20" s="28">
         <v>942432</v>
       </c>
-      <c r="M20" s="29">
+      <c r="M20" s="28">
         <v>941568</v>
       </c>
-      <c r="N20" s="30">
+      <c r="N20" s="29">
         <v>1035955.2</v>
       </c>
-      <c r="O20" s="30">
+      <c r="O20" s="29">
         <v>1226940</v>
       </c>
-      <c r="P20" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q20" s="27">
+      <c r="P20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q20" s="23">
         <v>4346572.8</v>
       </c>
-      <c r="R20" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="S20" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="T20" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="U20" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="V20" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="W20" s="26" t="s">
-        <v>134</v>
+      <c r="R20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/data/lot-details.xlsx
+++ b/data/lot-details.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="137">
   <si>
     <t>进口批次 / 货品</t>
   </si>
@@ -936,9 +936,6 @@
     </r>
   </si>
   <si>
-    <t>estimate 5/20</t>
-  </si>
-  <si>
     <t>Export lot 9</t>
   </si>
   <si>
@@ -1056,6 +1053,9 @@
       </rPr>
       <t>&lt;br&gt;电池电芯</t>
     </r>
+  </si>
+  <si>
+    <t>待付款</t>
   </si>
   <si>
     <t>待定 (TBD)</t>
@@ -1155,13 +1155,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="#\ ??/??"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1941,10 +1940,10 @@
     <xf numFmtId="8" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="8" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3544,11 +3543,11 @@
       <c r="D15" s="20">
         <v>279946.24</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="21" t="s">
         <v>111</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>112</v>
       </c>
       <c r="G15" s="9">
         <v>14</v>
@@ -3584,10 +3583,10 @@
         <v>329728</v>
       </c>
       <c r="R15" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="S15" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>114</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>107</v>
@@ -3599,29 +3598,29 @@
         <v>46175</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="15" spans="1:25">
       <c r="A16" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B16" s="13">
         <v>119976.96</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D16" s="12">
         <v>119976.96</v>
       </c>
-      <c r="E16" s="21" t="s">
-        <v>111</v>
+      <c r="E16" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G16" s="9">
         <v>6</v>
@@ -3657,13 +3656,13 @@
         <v>141312</v>
       </c>
       <c r="R16" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="S16" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="S16" s="9" t="s">
+      <c r="T16" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="T16" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="U16" s="14">
         <v>46182</v>
@@ -3679,18 +3678,20 @@
     </row>
     <row r="17" ht="15" spans="1:27">
       <c r="A17" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B17" s="13">
         <v>279946.24</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D17" s="12">
         <v>279946.24</v>
       </c>
-      <c r="E17" s="12"/>
+      <c r="E17" s="22" t="s">
+        <v>123</v>
+      </c>
       <c r="F17" s="9" t="s">
         <v>124</v>
       </c>
@@ -3761,7 +3762,9 @@
       <c r="D18" s="24">
         <v>279946.24</v>
       </c>
-      <c r="E18" s="24"/>
+      <c r="E18" s="22" t="s">
+        <v>123</v>
+      </c>
       <c r="F18" s="9" t="s">
         <v>124</v>
       </c>
@@ -3831,6 +3834,9 @@
       </c>
       <c r="D19" s="23">
         <v>279946.24</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>123</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>124</v>

--- a/data/lot-details.xlsx
+++ b/data/lot-details.xlsx
@@ -2069,8 +2069,10 @@
       <c r="U7" s="32" t="n">
         <v>46170</v>
       </c>
-      <c r="V7" s="10" t="n">
-        <v>20</v>
+      <c r="V7" s="10" t="inlineStr">
+        <is>
+          <t>已付</t>
+        </is>
       </c>
       <c r="W7" s="5" t="inlineStr">
         <is>
@@ -2160,7 +2162,11 @@
           <t>5月3日</t>
         </is>
       </c>
-      <c r="V8" s="5" t="n"/>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>已付</t>
+        </is>
+      </c>
       <c r="W8" s="5" t="inlineStr">
         <is>
           <t>已抵上海</t>
@@ -2245,7 +2251,11 @@
       <c r="U9" s="31" t="n">
         <v>46192</v>
       </c>
-      <c r="V9" s="5" t="n"/>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>已付</t>
+        </is>
+      </c>
       <c r="W9" s="5" t="inlineStr">
         <is>
           <t>已抵上海</t>
@@ -2334,7 +2344,11 @@
           <t>5月11日</t>
         </is>
       </c>
-      <c r="V10" s="5" t="n"/>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>已付</t>
+        </is>
+      </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
           <t>已抵上海</t>
@@ -2423,7 +2437,11 @@
           <t>5月11日</t>
         </is>
       </c>
-      <c r="V11" s="5" t="n"/>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>已付</t>
+        </is>
+      </c>
       <c r="W11" s="5" t="inlineStr">
         <is>
           <t>已抵上海</t>
@@ -2512,7 +2530,11 @@
           <t>5月11日</t>
         </is>
       </c>
-      <c r="V12" s="5" t="n"/>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>已付</t>
+        </is>
+      </c>
       <c r="W12" s="5" t="inlineStr">
         <is>
           <t>已抵上海</t>
